--- a/docs/baseline/output/00_검진_예약접수_업무정책.xlsx
+++ b/docs/baseline/output/00_검진_예약접수_업무정책.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1209" uniqueCount="499">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1217" uniqueCount="503">
   <si>
     <t>핵심 요약</t>
   </si>
@@ -641,6 +641,12 @@
 → 공통 업무 가능</t>
   </si>
   <si>
+    <t>적용 대상</t>
+  </si>
+  <si>
+    <t>예약·접수 업무에 적용한다. 기준정보 정비(수검자 Master·휴무일 Master)에는 적용하지 않는다 — 기준정보를 운영시간 안으로 묶으면 정비가 필요한 바로 그 시각에 막힌다.</t>
+  </si>
+  <si>
     <t>마감시간 추가 적용</t>
   </si>
   <si>
@@ -651,6 +657,12 @@
   </si>
   <si>
     <t>UI의 Enabled/Disabled는 사전안내이며, 저장·상태전이 시 DB에서 현재 조건을 다시 검증한다.</t>
+  </si>
+  <si>
+    <t>UI 차단 금지</t>
+  </si>
+  <si>
+    <t>UI는 공통 업무 불가를 안내로 표시하되 기능을 막지 않는다. 최종 권한이 Stored Procedure에 있으므로 화면이 미리 닫으면 그 판정을 받아볼 수 없다.</t>
   </si>
   <si>
     <t>수검자 식별정보 처리 원칙</t>
@@ -2871,7 +2883,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -3166,36 +3178,36 @@
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="s">
+      <c r="A22" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="B22" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C22" s="8" t="s">
+      <c r="D22" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="D22" s="8" t="s">
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="6" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C23" s="8" t="s">
+      <c r="D23" s="6" t="s">
         <v>214</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B24" s="8" t="s">
         <v>7</v>
@@ -3209,7 +3221,7 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B25" s="8" t="s">
         <v>7</v>
@@ -3223,7 +3235,7 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B26" s="8" t="s">
         <v>7</v>
@@ -3237,7 +3249,7 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B27" s="8" t="s">
         <v>7</v>
@@ -3251,7 +3263,7 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B28" s="8" t="s">
         <v>7</v>
@@ -3265,7 +3277,7 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B29" s="8" t="s">
         <v>7</v>
@@ -3277,8 +3289,36 @@
         <v>227</v>
       </c>
     </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>231</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:D29"/>
+  <autoFilter ref="A2:D31"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -3302,7 +3342,7 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3319,36 +3359,36 @@
         <v>4</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>7</v>
@@ -3371,16 +3411,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>7</v>
@@ -3403,16 +3443,16 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>46</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>7</v>
@@ -3435,16 +3475,16 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>7</v>
@@ -3467,16 +3507,16 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>7</v>
@@ -3499,16 +3539,16 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>7</v>
@@ -3531,16 +3571,16 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>7</v>
@@ -3563,16 +3603,16 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>7</v>
@@ -3595,16 +3635,16 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>7</v>
@@ -3627,16 +3667,16 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>7</v>
@@ -3659,16 +3699,16 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="E13" s="8" t="s">
         <v>7</v>
@@ -3691,16 +3731,16 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="E14" s="8" t="s">
         <v>7</v>
@@ -3723,16 +3763,16 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="E15" s="8" t="s">
         <v>7</v>
@@ -3755,16 +3795,16 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="E16" s="8" t="s">
         <v>7</v>
@@ -3787,16 +3827,16 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="E17" s="8" t="s">
         <v>7</v>
@@ -3819,16 +3859,16 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="E18" s="8" t="s">
         <v>7</v>
@@ -3851,16 +3891,16 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>48</v>
@@ -3883,7 +3923,7 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>7</v>
@@ -3892,13 +3932,13 @@
         <v>7</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="G20" s="9" t="s">
         <v>7</v>
@@ -3915,7 +3955,7 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>7</v>
@@ -3924,13 +3964,13 @@
         <v>7</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="G21" s="9" t="s">
         <v>7</v>
@@ -3947,7 +3987,7 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>7</v>
@@ -3956,13 +3996,13 @@
         <v>7</v>
       </c>
       <c r="D22" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>292</v>
+      </c>
+      <c r="F22" s="9" t="s">
         <v>293</v>
-      </c>
-      <c r="E22" s="9" t="s">
-        <v>288</v>
-      </c>
-      <c r="F22" s="9" t="s">
-        <v>289</v>
       </c>
       <c r="G22" s="9" t="s">
         <v>7</v>
@@ -3979,7 +4019,7 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>7</v>
@@ -3988,13 +4028,13 @@
         <v>7</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="G23" s="9" t="s">
         <v>7</v>
@@ -4011,16 +4051,16 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="B24" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="E24" s="8" t="s">
         <v>7</v>
@@ -4043,16 +4083,16 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="B25" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="E25" s="8" t="s">
         <v>7</v>
@@ -4075,16 +4115,16 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="B26" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="E26" s="8" t="s">
         <v>7</v>
@@ -4107,16 +4147,16 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="B27" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="E27" s="8" t="s">
         <v>7</v>
@@ -4139,16 +4179,16 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="B28" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="E28" s="8" t="s">
         <v>7</v>
@@ -4171,22 +4211,22 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="G29" s="4" t="s">
         <v>7</v>
@@ -4203,7 +4243,7 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>7</v>
@@ -4212,13 +4252,13 @@
         <v>7</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="G30" s="6" t="s">
         <v>7</v>
@@ -4235,7 +4275,7 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>7</v>
@@ -4244,13 +4284,13 @@
         <v>7</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="G31" s="6" t="s">
         <v>7</v>
@@ -4267,7 +4307,7 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>7</v>
@@ -4276,13 +4316,13 @@
         <v>7</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="G32" s="6" t="s">
         <v>7</v>
@@ -4299,7 +4339,7 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>7</v>
@@ -4308,13 +4348,13 @@
         <v>7</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="G33" s="6" t="s">
         <v>7</v>
@@ -4331,7 +4371,7 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>7</v>
@@ -4340,13 +4380,13 @@
         <v>7</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="G34" s="6" t="s">
         <v>7</v>
@@ -4363,16 +4403,16 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="E35" s="6" t="s">
         <v>7</v>
@@ -4395,16 +4435,16 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>7</v>
@@ -4427,16 +4467,16 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="E37" s="6" t="s">
         <v>7</v>
@@ -4459,22 +4499,22 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="G38" s="4" t="s">
         <v>7</v>
@@ -4491,7 +4531,7 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B39" s="8" t="s">
         <v>7</v>
@@ -4503,7 +4543,7 @@
         <v>24</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>24</v>
@@ -4523,7 +4563,7 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B40" s="8" t="s">
         <v>7</v>
@@ -4535,7 +4575,7 @@
         <v>24</v>
       </c>
       <c r="E40" s="10" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F40" s="10" t="s">
         <v>30</v>
@@ -4555,7 +4595,7 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B41" s="8" t="s">
         <v>7</v>
@@ -4567,7 +4607,7 @@
         <v>24</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>27</v>
@@ -4587,7 +4627,7 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B42" s="8" t="s">
         <v>7</v>
@@ -4599,7 +4639,7 @@
         <v>27</v>
       </c>
       <c r="E42" s="10" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="F42" s="10" t="s">
         <v>27</v>
@@ -4619,7 +4659,7 @@
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B43" s="8" t="s">
         <v>7</v>
@@ -4631,7 +4671,7 @@
         <v>27</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>33</v>
@@ -4651,16 +4691,16 @@
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="7" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B44" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="E44" s="8" t="s">
         <v>7</v>
@@ -4683,39 +4723,39 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B45" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B46" s="8" t="s">
         <v>7</v>
@@ -4730,24 +4770,24 @@
         <v>134</v>
       </c>
       <c r="F46" s="10" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="G46" s="10" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="H46" s="10" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="I46" s="10" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="J46" s="10" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B47" s="8" t="s">
         <v>7</v>
@@ -4762,24 +4802,24 @@
         <v>134</v>
       </c>
       <c r="F47" s="10" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="I47" s="10" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="J47" s="10" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B48" s="8" t="s">
         <v>7</v>
@@ -4791,27 +4831,27 @@
         <v>30</v>
       </c>
       <c r="E48" s="10" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="F48" s="10" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="G48" s="10" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="H48" s="10" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="I48" s="10" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="J48" s="10" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B49" s="8" t="s">
         <v>7</v>
@@ -4823,36 +4863,36 @@
         <v>33</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="F49" s="10" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="I49" s="10" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="J49" s="10" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B50" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="E50" s="8" t="s">
         <v>7</v>
@@ -4894,7 +4934,7 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4902,7 +4942,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>40</v>
@@ -4911,24 +4951,24 @@
         <v>4</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>7</v>
@@ -4939,16 +4979,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>7</v>
@@ -4959,16 +4999,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>7</v>
@@ -4979,16 +5019,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>7</v>
@@ -4999,16 +5039,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>7</v>
@@ -5019,7 +5059,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>7</v>
@@ -5028,7 +5068,7 @@
         <v>205</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>7</v>
@@ -5039,16 +5079,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="B9" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="E9" s="8" t="s">
         <v>7</v>
@@ -5059,16 +5099,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>7</v>
@@ -5079,16 +5119,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>7</v>
@@ -5099,16 +5139,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>7</v>
@@ -5119,16 +5159,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="C13" s="8" t="s">
+        <v>383</v>
+      </c>
+      <c r="D13" s="10" t="s">
         <v>379</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>375</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>7</v>
@@ -5139,16 +5179,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="E14" s="10" t="s">
         <v>7</v>
@@ -5159,16 +5199,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>7</v>
@@ -5179,16 +5219,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>7</v>
@@ -5199,16 +5239,16 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>7</v>
@@ -5219,16 +5259,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="E18" s="10" t="s">
         <v>7</v>
@@ -5239,16 +5279,16 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>155</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>7</v>
@@ -5259,16 +5299,16 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>7</v>
@@ -5279,16 +5319,16 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="E21" s="6" t="s">
         <v>7</v>
@@ -5299,16 +5339,16 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>7</v>
@@ -5319,16 +5359,16 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="E23" s="6" t="s">
         <v>7</v>
@@ -5339,16 +5379,16 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>7</v>
@@ -5359,16 +5399,16 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="E25" s="8" t="s">
         <v>7</v>
@@ -5379,16 +5419,16 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>7</v>
@@ -5399,16 +5439,16 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="E27" s="6" t="s">
         <v>7</v>
@@ -5419,16 +5459,16 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>7</v>
@@ -5442,19 +5482,19 @@
         <v>60</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -5462,19 +5502,19 @@
         <v>60</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="F30" s="10" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -5482,19 +5522,19 @@
         <v>60</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="C31" s="8" t="s">
+        <v>433</v>
+      </c>
+      <c r="D31" s="10" t="s">
         <v>429</v>
       </c>
-      <c r="D31" s="10" t="s">
-        <v>425</v>
-      </c>
       <c r="E31" s="10" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="F31" s="10" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -5502,19 +5542,19 @@
         <v>60</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="E32" s="10" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="F32" s="10" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -5522,19 +5562,19 @@
         <v>60</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="F33" s="10" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -5542,19 +5582,19 @@
         <v>60</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="F34" s="10" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -5562,19 +5602,19 @@
         <v>60</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="F35" s="10" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -5582,33 +5622,33 @@
         <v>60</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="F36" s="10" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="E37" s="6" t="s">
         <v>7</v>
@@ -5619,16 +5659,16 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>7</v>
@@ -5639,16 +5679,16 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="E39" s="6" t="s">
         <v>7</v>
@@ -5659,16 +5699,16 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>7</v>
@@ -5679,16 +5719,16 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="E41" s="6" t="s">
         <v>7</v>
@@ -5699,16 +5739,16 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>7</v>
@@ -5719,16 +5759,16 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="C43" s="8" t="s">
         <v>7</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="E43" s="8" t="s">
         <v>7</v>
@@ -5739,16 +5779,16 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="7" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="C44" s="8" t="s">
         <v>7</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="E44" s="8" t="s">
         <v>7</v>
@@ -5759,16 +5799,16 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="C45" s="8" t="s">
         <v>7</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="E45" s="8" t="s">
         <v>7</v>
@@ -5779,16 +5819,16 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="C46" s="8" t="s">
         <v>7</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="E46" s="8" t="s">
         <v>7</v>
@@ -5799,16 +5839,16 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="C47" s="8" t="s">
         <v>7</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="E47" s="8" t="s">
         <v>7</v>
@@ -5819,16 +5859,16 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="C48" s="8" t="s">
         <v>7</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="E48" s="8" t="s">
         <v>7</v>
@@ -5839,7 +5879,7 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="B49" s="8" t="s">
         <v>7</v>
@@ -5848,7 +5888,7 @@
         <v>205</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="E49" s="8" t="s">
         <v>7</v>
@@ -5859,16 +5899,16 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="B50" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="E50" s="8" t="s">
         <v>7</v>
@@ -5896,7 +5936,7 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -5907,216 +5947,216 @@
         <v>131</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>134</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>136</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>138</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>140</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>142</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>144</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>146</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>148</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>150</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="B12" s="8" t="s">
         <v>134</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="B13" s="8" t="s">
         <v>136</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="B14" s="8" t="s">
         <v>138</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="B15" s="8" t="s">
         <v>140</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="B16" s="8" t="s">
         <v>142</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="B17" s="8" t="s">
         <v>144</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="B18" s="8" t="s">
         <v>146</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="B19" s="8" t="s">
         <v>148</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="B20" s="8" t="s">
         <v>150</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="B21" s="8" t="s">
         <v>152</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
     </row>
   </sheetData>
